--- a/www/download/COUNTRY.CYP.EXI382.xlsx
+++ b/www/download/COUNTRY.CYP.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Chipre</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2197490797546</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21891656441718</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.506</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.264</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.268</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.277</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.279</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.291</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.306</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.316</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.326</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.337</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.349</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.357</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.378</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.402</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.392</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.362</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.362</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.428</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.472</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.495</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.509</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.433</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.207</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.209</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.211</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.213</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.213</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.221</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.234</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.243</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.249</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.258</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.268</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.312</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.313</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.327</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.328</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.326</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.302</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.304</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.371</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.434</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1024.903</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>550.339</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>558.81</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>567.856</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>576.647</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>580.265</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>604.433</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>620.968</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>638.417</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>655.987</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>686.864</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>718.428</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>735.148</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>774.107</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>796.951</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>786.771</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>814.256</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>805.886</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>790.685</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>728.828</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>734.061</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>770.833</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>868.364</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>891.839</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>955.443</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>999.765</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1028.557</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>878.89</t>
+          <t>1147473986.12352</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>289.225</t>
+          <t>989998206.981097</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>288.362</t>
+          <t>905720352.58641</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>287.766</t>
+          <t>917596148.109895</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>285.743</t>
+          <t>1004630570.51707</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>279.239</t>
+          <t>1021926445.00651</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>446.961</t>
+          <t>1165415272.14103</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>465.886</t>
+          <t>1155423704.25409</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>480.868</t>
+          <t>1144684064.0999</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>488.708</t>
+          <t>1073165799.21042</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>510.342</t>
+          <t>1118333617.06794</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>535.657</t>
+          <t>923805544.887432</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>559.224</t>
+          <t>821782392.31363</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>603.268</t>
+          <t>1111554718.81303</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>629.667</t>
+          <t>1032162805.79236</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>624.836</t>
+          <t>1046732423.90066</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>660.188</t>
+          <t>945511564.074656</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>661.555</t>
+          <t>941483756.487986</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>660.796</t>
+          <t>835632234.669899</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>612.347</t>
+          <t>729654588.467901</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>618.385</t>
+          <t>686127180.327539</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>651.734</t>
+          <t>756638487.596398</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>734.15</t>
+          <t>751516040.902647</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>757.545</t>
+          <t>848421103.520351</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>811.665</t>
+          <t>825933219.548791</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>852.762</t>
+          <t>917139268.296021</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>880.132</t>
+          <t>735343013.139555</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>589104507.60973</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>601675218.852194</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>469949241.251025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>556296765.183439</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>572272606.572987</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>621223363.518547</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>533344713.654339</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>486165552.60562</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>522047595.09559</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>458185060.70964</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>452054318.862723</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>334847259.288668</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>297580852.540648</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>314073409.21233</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>438024275.029108</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>357862393.393087</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>262075487.553218</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>291230051.763959</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>293931972.379671</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>241061233.929738</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>267661282.633232</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>297608977.855198</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>284587797.129412</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>285438427.584296</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>314195276.701261</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>320021814.061232</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>139729384.35506</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>36848936.1433097</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10946436752.9359</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12306930.734941</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10760225.1530261</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10194337.0149892</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10817745.0051483</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15478765.4006008</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>12629494.3845492</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>11819704.3704056</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10765947.9068601</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>8379158.93297928</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>436088334.694228</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6395515.01765503</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>471467062.862278</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6747046.88551398</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6689968.76602279</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7230583.48361542</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7976987.42488029</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6220474.81748632</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>9107146085.84462</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>5870794404.01711</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>39600954045.0053</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>6013427067.50947</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5608483.41424682</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>4457023.62994064</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>5201842.64502584</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5121225.51885597</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1493.79837134516</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1922.89175049341</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2097.27123349426</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2166.96975687412</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2285.04351098543</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2714.84332395862</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2792.63660915219</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2847.97886755061</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2633.45031910222</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2618.00703761222</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3040.81272251802</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3376.09682416247</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3488.85939393602</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3714.59621013171</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3881.99519319745</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4287.93610053706</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4510.35058923702</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4865.15381953354</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>4505.32505810622</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>4256.08869187179</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>4291.85559562859</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>4193.90907028152</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>4977.07245742268</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5211.119754698</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>5911.71409328252</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>6031.63471826184</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>5860.07346648598</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4277.32706176845</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7523.06808005066</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7496.30682457825</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7807.77150525458</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9016.85558219547</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10964.0582080262</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12554.7291001555</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>12065.6699892585</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>10980.7041721155</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10060.3088507744</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>11238.9976216259</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>9931.19589617085</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>9152.94009143738</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>12439.9752272409</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>11575.8597646525</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>13537.7669856157</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>12730.6615346379</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13991.7187918737</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>12130.8558103576</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>10963.9641155335</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>11646.4237148805</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>11706.2852755619</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>12292.616005173</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13497.0686885696</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>13999.4613082209</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14788.3727123433</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>11640.9653429078</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.491908053879914</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.519300461548118</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.386397562357011</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.482711354783898</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.500687265617639</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.550501451815706</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.161966007054882</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.0417132651561739</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.0788809209779975</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0666170547835765</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.128939551521235</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.599705492999694</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.879233812342148</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.920786613273385</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.437516219753229</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.746023084671722</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.51907572953004</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.27158906161307</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.24812562801563</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.54021204759548</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.31032637211977</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.18989978266547</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.579694684438</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.65396982423446</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.58331271110176</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.66470059508697</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5.29883456804677</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1361.45541906395</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2905.24007171524</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2246.94832058922</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2631.48895545559</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2683.57611523016</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2922.02899114999</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2416.60495538899</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2077.63056668992</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2146.57728246508</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1838.62383912387</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1752.82791338811</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1250.36317882251</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1064.30920078942</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1045.16941501611</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1404.82448694432</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1144.42722543351</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>801.454090376755</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>888.980621989926</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>901.355327751442</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>797.162994188467</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>881.327186885436</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>931.294652457832</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>790.797987455442</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>768.738703117351</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>787.271715752231</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>761.654125396288</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>321.72929509358</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1049032498.96896</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>981638836.371885</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>727102260.598182</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>886906557.208977</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>985679274.63159</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>994602977.917506</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1135903594.75036</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>988227999.042761</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>773911718.99237</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>740014533.217414</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>650485573.01441</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>471592237.182877</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>290698813.99445</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>291486537.989412</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>500151858.826756</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>552041762.382083</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>449861055.137963</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>541993002.005458</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>498315638.776783</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>572139345.418662</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>549827558.602234</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>549560156.611859</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>516071215.412377</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>533073133.954861</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>509590353.361029</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>561414153.043616</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>90430337.4895838</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11288974.5415906</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>547875818.569877</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>297460213.470185</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>427201688.141692</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>482294081.745782</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>477249645.006556</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>487481388.261807</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>468509610.849529</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>254448960.864529</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>225765292.87436</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>204580525.791295</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>133110521.916841</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>36556239.835331</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>176740721.421526</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>141793496.985659</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>218550400.287203</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>142387609.677548</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>192716628.314533</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>110276873.055722</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>180952913.853926</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>154676095.85355</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>106860293.443562</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>220515571.202522</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>208124952.357457</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>206113459.658948</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>227528422.338498</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>113205467.871414</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1037743524.42737</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>433763017.802008</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>429642047.127997</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>459704869.067285</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>503385192.885807</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>517353332.91095</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>648422206.488551</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>519718388.193232</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>519462758.127841</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>514249240.343053</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>445905047.223115</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>338481715.266035</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>254142574.159119</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>114745816.567887</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>358358361.841097</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>333491362.09488</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>307473445.460415</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>349276373.690925</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>388038765.721061</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>391186431.564736</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>395151462.748684</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>442699863.168297</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>295555644.209855</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>324948181.597403</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>303476893.702081</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>333885730.705118</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-22775130.3818306</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2031.16630469997</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1396.54756156543</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1378.73296677137</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1361.23935666876</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1339.94372801876</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1313.44778927434</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2025.19710013559</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1990.96581196501</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1977.25328947379</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1961.10754414117</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1978.83675843427</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2000.21284540692</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>2000.08583691032</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2007.54742096571</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2019.45798588897</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1998.19635433372</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2018.92354740066</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2019.3986568983</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>2026.36001226644</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>2024.96304173483</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>2036.15344232755</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2039.44195701492</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2040.01736470308</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>2040.20932079459</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2033.76903039363</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>2029.58020119394</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>2026.51960548876</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2023.73881906659</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2085.40735126997</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2084.5285834198</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2083.4929370746</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2082.32192831992</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2082.78894472263</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2073.52658662061</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2029.97057862011</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2019.02909550934</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2009.76409313747</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2036.35932404434</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2059.12295786754</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2060.9700028037</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2049.52872650297</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2042.94027172566</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2018.91454965389</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2027.02514314179</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2018.24693213121</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2018.59841715626</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2015.99399669507</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2027.9107400453</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2028.49086893262</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2027.73898003484</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2025.89460445022</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2022.28984967803</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2020.05030899962</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2019.16064215254</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5335.36487462828</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5879.98641242739</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6092.41658585612</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6104.27805682318</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6913.32858291875</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7974.96082361274</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8055.54600785975</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6948.12888306045</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>6595.7426892012</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6019.38706685878</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>5606.35529752372</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5023.98120463781</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5018.37129419691</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3864.12684114778</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6432.66795452437</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>7067.62667447119</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>7152.41842010536</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>8393.9091263091</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>8933.88745007806</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>9941.1058604387</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>11946.5761124172</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>13073.1514446322</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>12680.2005584532</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12877.0528095975</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>13090.4441249268</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13682.5823604843</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3471.71680215138</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>311375500.498684</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>280538397.809187</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>267873872.354608</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>259339825.772494</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>286720287.754333</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>296937638.943507</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>269926324.261573</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>263464962.088343</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>192064659.1961</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>161653023.804289</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>159371152.627471</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>108274589.177866</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>93736148.5431301</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>101174454.39564</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>132598873.861634</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>138049408.115118</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>139510724.398109</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>151112037.018522</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>175320740.989842</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>188290255.266852</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>186857451.961239</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>203198623.606984</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>186151435.83691</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>181372472.179855</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>163698073.166864</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>187665094.00593</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>47740771.8396552</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5421.13300790423</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5924.72404428716</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>6245.58944428738</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5807.44358349634</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6572.94172687997</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>7631.91776643322</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7362.26849843238</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6763.98457042954</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>6340.44646163149</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6041.97674939498</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5710.97306025438</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5647.87504043651</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6110.30409940346</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>7024.5775746405</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7733.44720889171</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>9183.37195784091</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>8142.28705785861</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>8880.51132990486</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>8561.99309253937</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>9727.53108882633</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>11334.8054446538</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>12653.5674286585</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>12778.2990678473</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12659.6717446372</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>13203.1913248104</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13859.9753861914</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3692.16990485054</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1024.903</t>
+          <t>1408997897.49841</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>550.339</t>
+          <t>1271265149.42576</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>558.81</t>
+          <t>1023648210.65749</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>567.856</t>
+          <t>1090323266.73232</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>576.647</t>
+          <t>1209957672.43706</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>580.265</t>
+          <t>1238320718.5606</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>604.433</t>
+          <t>1294018823.50138</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>620.968</t>
+          <t>1220879439.44851</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>638.417</t>
+          <t>922607253.184119</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>655.987</t>
+          <t>905810275.324934</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>686.864</t>
+          <t>827354107.588493</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>718.428</t>
+          <t>672697050.555513</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>735.148</t>
+          <t>520033803.314305</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>774.107</t>
+          <t>825767104.862681</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>796.951</t>
+          <t>824214265.217119</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>786.771</t>
+          <t>950966830.093213</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>814.256</t>
+          <t>703519229.153281</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>805.886</t>
+          <t>746159876.554515</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>790.685</t>
+          <t>631034558.353717</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>728.828</t>
+          <t>737725301.249947</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>734.061</t>
+          <t>677548270.29523</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>770.833</t>
+          <t>708259154.710706</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>868.364</t>
+          <t>711671770.133986</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>891.839</t>
+          <t>692840165.964667</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>955.443</t>
+          <t>683578571.006036</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>999.765</t>
+          <t>766293701.563093</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1028.557</t>
+          <t>159650973.701158</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>878.89</t>
+          <t>-85.768133275947</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>289.225</t>
+          <t>-44.7376318597711</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>288.362</t>
+          <t>-153.172858431252</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>287.766</t>
+          <t>296.834473326839</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>285.743</t>
+          <t>340.38685603878</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>279.239</t>
+          <t>343.043057179516</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>446.961</t>
+          <t>693.277509427377</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>465.886</t>
+          <t>184.144312630911</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>480.868</t>
+          <t>255.296227569712</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>488.708</t>
+          <t>-22.5896825362038</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>510.342</t>
+          <t>-104.617762730664</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>535.657</t>
+          <t>-623.893835798703</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>559.224</t>
+          <t>-1091.93280520655</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>603.268</t>
+          <t>-3160.45073349272</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>629.667</t>
+          <t>-1300.77925436734</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>624.836</t>
+          <t>-2115.74528336972</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>660.188</t>
+          <t>-989.868637753255</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>661.555</t>
+          <t>-486.602203595766</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>660.796</t>
+          <t>371.894357538686</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>612.347</t>
+          <t>213.574771612376</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>618.385</t>
+          <t>611.770667763367</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>651.734</t>
+          <t>419.584015973692</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>734.15</t>
+          <t>-98.0985093941689</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>757.545</t>
+          <t>217.381064960355</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>811.665</t>
+          <t>-112.747199883627</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>852.762</t>
+          <t>-177.39302570713</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>880.132</t>
+          <t>-220.453102699165</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>915.892</t>
+          <t>-1097622396.99973</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>783.801</t>
+          <t>-990726751.616568</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>718.125</t>
+          <t>-755774338.302879</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>734.315</t>
+          <t>-830983440.959831</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>792.381</t>
+          <t>-923237384.682728</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>808.632</t>
+          <t>-941383079.617098</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>914.757</t>
+          <t>-1024092499.2398</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>913.041</t>
+          <t>-957414477.360171</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>910.474</t>
+          <t>-730542593.988019</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>858.214</t>
+          <t>-744157251.520645</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>881.875</t>
+          <t>-667982954.961022</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>741.98</t>
+          <t>-564422461.377647</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>666.206</t>
+          <t>-426297654.771174</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>876.608</t>
+          <t>-724592650.467041</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>821.74</t>
+          <t>-691615391.355485</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>822.015</t>
+          <t>-812917421.978095</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>750.59</t>
+          <t>-564008504.755171</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>741.727</t>
+          <t>-595047839.535992</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>658.328</t>
+          <t>-455713817.363875</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>579.344</t>
+          <t>-549435045.983095</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>548.861</t>
+          <t>-490690818.333992</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>603.398</t>
+          <t>-505060531.103722</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>607.257</t>
+          <t>-525520334.297076</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>674.502</t>
+          <t>-511467693.784812</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>663.879</t>
+          <t>-519880497.839172</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>731.607</t>
+          <t>-578628607.557164</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>617.614</t>
+          <t>-111910201.861503</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1958.23174648796</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2522.01864995878</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2540.79000418746</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2925.89060569815</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3033.9416850187</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3280.55335254262</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3202.06222319791</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3412.75480100832</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4026.84672835825</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4218.71553030922</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4505.02934996643</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4957.36508510119</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5325.85806966721</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5469.79555016451</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>5212.05381229295</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5346.91270598321</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5099.50135674446</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4938.43941884919</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4564.35766972086</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3953.31539204959</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4473.81505560638</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4750.79621490086</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4925.33972307944</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5491.77868149703</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>6348.34285159278</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>5500.38932489678</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6503.98759502003</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>400.74</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>253.043</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>253.397</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>254.67</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>254.593</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>253.042</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>259.232</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>272.726</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>274.524</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>279.271</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>302.575</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>314.046</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>313.242</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>331.912</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>346.139</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>331.541</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>334.986</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>327.37</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>310.349</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>283.244</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>252.847</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>271.074</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>304.276</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>327.569</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>348.776</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>374.067</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>370.172</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3775.97036719255</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4396.1098510705</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4773.45055706021</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>5518.59681756397</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>5714.36621945998</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6664.04031303083</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6323.67865270112</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6921.64758087576</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>7831.89439344073</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>7974.29927829446</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>8828.01157329718</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>9837.50467673848</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>10448.3469233734</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>10334.6285670715</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>10877.3709448485</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10446.4251000842</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10271.5244316107</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10055.0231504971</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>9900.81623755864</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>8552.48090032617</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>9329.45351161145</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10116.7592007911</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>9658.08346272405</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10994.9234640065</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>11874.9497812925</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>11190.7304835376</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>12532.3412619706</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>539.328</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>553.603</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>436.263</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>516.108</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>522.79</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>563.194</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>481.307</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>443.814</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>476.372</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>417.254</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>408.148</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>302.4</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>271.019</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>283.882</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>396.073</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>316.809</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>234.035</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>255.004</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>255.804</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>211.139</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>236.619</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>261.887</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>253.95</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>249.506</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>277.805</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>282.376</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>131.496</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>62.96</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-47.76</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-33.9</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-44.24</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-45.34</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-50.42</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-7.14</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>4.97</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>25.04</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>77.14</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>106.34</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>112.51</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>58.98</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>97.23</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>182.09</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>159.43</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>158.32</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>190.02</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>161.34</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>148.86</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>189.09</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>203.62</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>192.17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>569.32</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>44.167</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>13896.842</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>11.874</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>11.191</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>17.375</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>13.875</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>13.267</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>11.828</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>8.985</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>552.456</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>7.071</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>597.337</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>7.366</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>7.376</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>7.826</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>8.953</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>6.735</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>11562.325</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>7453.299</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>50280.459</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>7634.517</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>6.238</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>5.752</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>5.902</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4408.04465760478</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4237.53217056022</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4686.20966723002</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4337.91355126114</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>5062.97822292419</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5001.08529644217</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6312.34618004265</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6462.46233085106</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5948.46137191313</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>7397.08951404104</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>7588.14928068875</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>7856.00660554014</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>8648.59967994023</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>10331.6173323076</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>9666.88092906627</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>10855.7022704264</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>11392.0703603963</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>11207.879155731</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>9314.88298489515</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>10426.2654001772</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>10190.0911065156</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>10094.83891011</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>12366.1472943985</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12223.5144257985</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>12239.1005963271</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13635.3149048437</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>12348.9387919883</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>878889759.479918</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>289225000.000184</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>288362000.000102</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>287765999.999841</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>285743000.000079</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>279238999.999751</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>446960999.999916</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>465885999.999984</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>480868000.000102</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>488707999.99995</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>510342000.00012</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>535656999.999975</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>559223999.999988</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>603268000.000177</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>629666999.999991</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>624836000.000203</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>660188000.000062</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>661555000.000017</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>660795999.999921</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>612346650.636553</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>618384920.062959</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>651733835.924391</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>734149627.510666</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>757544973.485657</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>811664652.070503</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>852762318.369777</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>880132276.347546</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1024902967.85932</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>550339000.000105</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>558810000.000059</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>567855999.999809</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>576647000.000091</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>580264999.999769</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>604432999.999886</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>620968000.000055</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>638417000.000103</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>655987000.000023</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>686864000.000062</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>718428000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>735147999.999951</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>774107000.000145</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>796951000.000003</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>786771000.000135</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>814256000.000087</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>805886000.000032</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>790684999.99994</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>728828094.964939</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>734060734.740077</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>770833001.495182</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>868364471.523196</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>891838971.554538</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>955442684.811026</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>999765279.808281</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1028556994.33781</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>400739701.893071</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>253042956.005576</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>253396944.058067</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>254669735.229846</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>254592584.429379</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>253042270.860227</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>259231507.735662</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>272726031.43565</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>274524162.260018</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>279271308.319858</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>302575301.222266</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>314046465.18358</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>313241777.019473</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>331911991.015491</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>346138527.258103</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>331540774.251416</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>334985627.302348</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>327369593.54605</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>310348660.067754</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>283243780.28115</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>252846611.998078</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>271074293.967461</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>304276143.248424</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>327569198.532852</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>348776352.647907</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>374067462.305593</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>370172400.065626</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>506440.336175415</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>263899.999999981</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>268074.999999902</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>272550.000000061</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>276925.000000047</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>278600.000000022</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>291499.99999999</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>305900.00000008</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>316200.000000024</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>326399.999999976</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>337299.999999954</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>348900.000000008</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>356699.999999937</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>377699.999999988</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>390099.999999914</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>389700.000000006</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>401700.000000015</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>399300.000000019</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>391699.999999917</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>361522.949056271</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>361978.819010386</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>380003.190204543</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>428242.727527128</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>440219.826636322</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>472455.857385203</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>494920.980608346</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>509398.297919137</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>432702.018267156</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>207099.999999989</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>209149.999999906</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>211400.000000048</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>213250.000000058</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>212600.00000002</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>220699.999999996</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>234000.000000087</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>243200.000000039</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>249199.999999985</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>257899.99999996</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>267800.000000001</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>279599.999999931</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>300499.99999999</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>311799.999999906</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>312700.000000024</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>327000.000000024</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>327600.000000067</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>326099.999999918</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>302398.9268031</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>303702.514362609</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>319564.787653147</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>359874.205098995</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>371307.476034185</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>399093.820360421</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>420166.849217451</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>434307.308926959</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1024902967.85932</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>550339000.000105</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>558810000.000059</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>567855999.999809</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>576647000.000091</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>580264999.999769</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>604432999.999886</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>620968000.000055</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>638417000.000103</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>655987000.000023</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>686864000.000062</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>718428000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>735147999.999951</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>774107000.000145</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>796951000.000003</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>786771000.000135</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>814256000.000087</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>805886000.000032</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>790684999.99994</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>728828094.964939</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>734060734.740077</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>770833001.495182</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>868364471.523196</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>891838971.554538</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>955442684.811026</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>999765279.808281</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1028556994.33781</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>878889759.479918</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>289225000.000184</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>288362000.000102</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>287765999.999841</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>285743000.000079</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>279238999.999751</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>446960999.999916</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>465885999.999984</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>480868000.000102</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>488707999.99995</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>510342000.00012</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>535656999.999975</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>559223999.999988</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>603268000.000177</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>629666999.999991</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>624836000.000203</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>660188000.000062</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>661555000.000017</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>660795999.999921</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>612346650.636553</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>618384920.062959</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>651733835.924391</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>734149627.510666</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>757544973.485657</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>811664652.070503</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>852762318.369777</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>880132276.347546</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13904.6785779279</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>15187.061840926</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>16024.3725688523</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>17090.1746717973</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>18589.3421832788</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>20691.1301419956</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>22131.4326853904</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>22453.2541080813</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24933.5303929859</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>26409.8249414399</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>27824.3529280982</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>29902.516880429</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>32774.0077219302</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>33829.1280062003</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>34681.9341234074</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>35499.9376077861</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>35228.0573745961</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>34692.4789337632</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>32049.234143152</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>31370.9157231393</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>32840.9826920421</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>35872.5350230286</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>38093.8174407546</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>41046.0187968421</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>42748.5301890244</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>43903.8085200079</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>41425.3334343181</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4371.57306371842</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4877.86784214894</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5008.72235657054</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6195.92016023624</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6275.90556441137</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7419.85046600106</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7040.88059388494</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>7393.48427464548</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>8845.065016218</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>8635.13236929557</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>9719.05576583727</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>10835.6258268921</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>11528.210915773</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>11419.375598685</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>11696.1831953596</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>11408.8484840956</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>11292.7231458168</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>11086.3383922183</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>11317.5648239052</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>9507.56698760539</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>10256.0137159192</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>11566.7853112412</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>10652.6654111459</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12048.3429253252</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>12959.6974173001</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12288.1503574079</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>14284.43341825</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
